--- a/doctool/Excel設計書レビュー指摘事項抽出ツール/レビュー記録サマリ.xlsx
+++ b/doctool/Excel設計書レビュー指摘事項抽出ツール/レビュー記録サマリ.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A045EE-3E34-4828-A8EA-3776A2166E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A79188-B257-4085-89C5-A19A8ADDCE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品質指標" sheetId="4" r:id="rId1"/>
@@ -13,12 +13,12 @@
     <sheet name="List" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">レビュー記録一覧!$A$5:$AR$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">レビュー記録一覧!$A$5:$BB$5</definedName>
     <definedName name="Method">List!$C$2:$C$3</definedName>
     <definedName name="Necessity">List!$F$2:$F$3</definedName>
     <definedName name="Person">List!#REF!</definedName>
     <definedName name="Phase">List!$A$2:$A$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー記録一覧!$A$1:$AN$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー記録一覧!$A$1:$AX$23</definedName>
     <definedName name="Result">List!$E$2:$E$4</definedName>
     <definedName name="Time">List!$D$2:$D$3</definedName>
     <definedName name="Volume">List!$B$2:$B$4</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="88">
   <si>
     <t>対象成果物</t>
     <rPh sb="0" eb="2">
@@ -52,16 +52,6 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ブツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>指摘事項</t>
-    <rPh sb="0" eb="2">
-      <t>シテキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジコウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -675,6 +665,32 @@
   </si>
   <si>
     <t>i)93_仕様変更</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>未済指摘事項</t>
+    <rPh sb="0" eb="2">
+      <t>ミサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全指摘事項</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジコウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -757,7 +773,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,6 +810,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -975,7 +997,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1062,7 +1084,7 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1111,6 +1133,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1119,15 +1152,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_レビュー記録サマリ_20130709" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor indexed="22"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="lightTrellis">
@@ -1150,9 +1175,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1190,9 +1215,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1225,26 +1250,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1277,26 +1285,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1487,50 +1478,50 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="25" t="s">
         <v>53</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1541,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G7" s="22">
@@ -1551,14 +1542,14 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1569,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G8" s="22">
@@ -1579,14 +1570,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1597,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G9" s="22">
@@ -1607,14 +1598,14 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1625,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G10" s="22">
@@ -1635,14 +1626,14 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1653,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G11" s="22">
@@ -1674,7 +1665,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
@@ -1701,63 +1692,65 @@
     <col min="26" max="27" width="9.25" style="1" customWidth="1"/>
     <col min="28" max="28" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="37" width="11.125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="11.25" style="1" customWidth="1"/>
-    <col min="39" max="39" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="39.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.125" style="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="9" style="1"/>
+    <col min="38" max="38" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="47" width="11.125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="11.25" style="1" customWidth="1"/>
+    <col min="49" max="49" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="39.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="AM1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="AW2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AN1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="AM2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.15">
+      <c r="AX2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="D3" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" s="37"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
       <c r="AA3" s="21"/>
-      <c r="AP3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AZ3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>0</v>
@@ -1776,7 +1769,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
@@ -1788,155 +1781,197 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="64" t="s">
+      <c r="AB4" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC4" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD4" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="AD4" s="66" t="s">
+      <c r="AE4" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="AE4" s="66" t="s">
+      <c r="AF4" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG4" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="AF4" s="66" t="s">
+      <c r="AH4" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI4" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ4" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK4" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL4" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM4" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="AG4" s="66" t="s">
+      <c r="AN4" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO4" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP4" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ4" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR4" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="AH4" s="66" t="s">
+      <c r="AS4" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="AI4" s="66" t="s">
+      <c r="AT4" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="AJ4" s="66" t="s">
+      <c r="AU4" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="AK4" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="6"/>
-      <c r="AO4" s="10"/>
-      <c r="AP4" s="31" t="s">
+      <c r="AV4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="AQ4" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="AR4" s="34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" ht="27" x14ac:dyDescent="0.15">
+      <c r="BB4" s="34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
       <c r="P5" s="63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="9"/>
       <c r="W5" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="17"/>
       <c r="Y5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB5" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="69"/>
+      <c r="AE5" s="69"/>
+      <c r="AF5" s="69"/>
+      <c r="AG5" s="69"/>
+      <c r="AH5" s="69"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="69"/>
+      <c r="AK5" s="69"/>
+      <c r="AL5" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM5" s="65"/>
+      <c r="AN5" s="66"/>
+      <c r="AO5" s="66"/>
+      <c r="AP5" s="66"/>
+      <c r="AQ5" s="66"/>
+      <c r="AR5" s="66"/>
+      <c r="AS5" s="66"/>
+      <c r="AT5" s="66"/>
+      <c r="AU5" s="66"/>
+      <c r="AV5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="Z5" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB5" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM5" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO5" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP5" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ5" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR5" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.15">
+      <c r="AW5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AY5" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="AZ5" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA5" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB5" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A6" s="40">
         <f t="shared" ref="A6" si="0">ROW()-5</f>
         <v>1</v>
       </c>
       <c r="B6" s="41" t="str">
-        <f>IF(C6&lt;&gt;"",IF(OR(AND(AL6&lt;&gt;"",AL6&lt;&gt;"再レビュー要"),COUNTIF(I$6:I16,A6)&gt;0),"○",""),"")</f>
+        <f>IF(C6&lt;&gt;"",IF(OR(AND(AV6&lt;&gt;"",AV6&lt;&gt;"再レビュー要"),COUNTIF(I$6:I16,A6)&gt;0),"○",""),"")</f>
         <v/>
       </c>
       <c r="C6" s="42"/>
@@ -1948,12 +1983,12 @@
       <c r="I6" s="46"/>
       <c r="J6" s="47"/>
       <c r="K6" s="45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="49"/>
       <c r="N6" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O6" s="49"/>
       <c r="P6" s="51">
@@ -1989,43 +2024,60 @@
       <c r="AI6" s="59"/>
       <c r="AJ6" s="59"/>
       <c r="AK6" s="59"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="60"/>
-      <c r="AO6" s="61"/>
-      <c r="AP6" s="62" t="str">
-        <f t="shared" ref="AP6" si="3">IF(J6&lt;&gt;"",AA6/(J6*AO6/10),"")</f>
+      <c r="AL6" s="58">
+        <f t="shared" ref="AL6" si="3">SUM(AM6:AU6)</f>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="42"/>
+      <c r="AW6" s="42"/>
+      <c r="AX6" s="60"/>
+      <c r="AY6" s="61"/>
+      <c r="AZ6" s="62" t="str">
+        <f>IF(J6&lt;&gt;"",AA6/(J6*AY6/10),"")</f>
         <v/>
       </c>
-      <c r="AQ6" s="62" t="str">
-        <f t="shared" ref="AQ6" si="4">IF(J6&lt;&gt;"",AB6/(J6*AO6/10),"")</f>
+      <c r="BA6" s="62" t="str">
+        <f>IF(J6&lt;&gt;"",AB6/(J6*AY6/10),"")</f>
         <v/>
       </c>
-      <c r="AR6" s="2" t="str">
-        <f t="shared" ref="AR6" si="5">IF(H6=1,J6*AO6,"")</f>
+      <c r="BB6" s="2" t="str">
+        <f t="shared" ref="BB6" si="4">IF(H6=1,J6*AY6,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AR5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <mergeCells count="9">
+  <autoFilter ref="A5:BB5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <mergeCells count="18">
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="AT4:AT5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="AM6:AQ6 A6:AK6">
-    <cfRule type="expression" dxfId="1" priority="105" stopIfTrue="1">
-      <formula>$B6="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL6">
+  <conditionalFormatting sqref="A6:BA6">
     <cfRule type="expression" dxfId="0" priority="103" stopIfTrue="1">
       <formula>$B6="○"</formula>
     </cfRule>
@@ -2040,15 +2092,15 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y6" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>Method</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM6" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW6" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>Necessity</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL6" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV6" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>Result</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.46" right="0.43" top="0.66" bottom="0.49" header="0.51200000000000001" footer="0.28999999999999998"/>
-  <pageSetup paperSize="9" scale="34" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="26" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader xml:space="preserve">&amp;R【&amp;U関係者外秘：SSMSアプリ開発PJメンバー限り&amp;U】 </oddHeader>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
@@ -2068,103 +2120,103 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/doctool/Excel設計書レビュー指摘事項抽出ツール/レビュー記録サマリ.xlsx
+++ b/doctool/Excel設計書レビュー指摘事項抽出ツール/レビュー記録サマリ.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A79188-B257-4085-89C5-A19A8ADDCE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6CAD9-28E1-4B4D-BD2A-26872ABD232D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1126,6 +1126,17 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1133,17 +1144,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1781,64 +1781,64 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="67" t="s">
+      <c r="AB4" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="AC4" s="68" t="s">
+      <c r="AC4" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="AD4" s="69" t="s">
+      <c r="AD4" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="AE4" s="69" t="s">
+      <c r="AE4" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="AF4" s="69" t="s">
+      <c r="AF4" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="AG4" s="69" t="s">
+      <c r="AG4" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="AH4" s="69" t="s">
+      <c r="AH4" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="AI4" s="69" t="s">
+      <c r="AI4" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="AJ4" s="69" t="s">
+      <c r="AJ4" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="AK4" s="69" t="s">
+      <c r="AK4" s="66" t="s">
         <v>85</v>
       </c>
       <c r="AL4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="AM4" s="64" t="s">
+      <c r="AM4" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="AN4" s="66" t="s">
+      <c r="AN4" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="AO4" s="66" t="s">
+      <c r="AO4" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="AP4" s="66" t="s">
+      <c r="AP4" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="AQ4" s="66" t="s">
+      <c r="AQ4" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="AR4" s="66" t="s">
+      <c r="AR4" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="AS4" s="66" t="s">
+      <c r="AS4" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="AT4" s="66" t="s">
+      <c r="AT4" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="AU4" s="66" t="s">
+      <c r="AU4" s="71" t="s">
         <v>85</v>
       </c>
       <c r="AV4" s="7" t="s">
@@ -1919,30 +1919,30 @@
       <c r="AA5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AB5" s="70" t="s">
+      <c r="AB5" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="AC5" s="71"/>
-      <c r="AD5" s="69"/>
-      <c r="AE5" s="69"/>
-      <c r="AF5" s="69"/>
-      <c r="AG5" s="69"/>
-      <c r="AH5" s="69"/>
-      <c r="AI5" s="69"/>
-      <c r="AJ5" s="69"/>
-      <c r="AK5" s="69"/>
+      <c r="AC5" s="68"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
       <c r="AL5" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="AM5" s="65"/>
-      <c r="AN5" s="66"/>
-      <c r="AO5" s="66"/>
-      <c r="AP5" s="66"/>
-      <c r="AQ5" s="66"/>
-      <c r="AR5" s="66"/>
-      <c r="AS5" s="66"/>
-      <c r="AT5" s="66"/>
-      <c r="AU5" s="66"/>
+      <c r="AM5" s="70"/>
+      <c r="AN5" s="71"/>
+      <c r="AO5" s="71"/>
+      <c r="AP5" s="71"/>
+      <c r="AQ5" s="71"/>
+      <c r="AR5" s="71"/>
+      <c r="AS5" s="71"/>
+      <c r="AT5" s="71"/>
+      <c r="AU5" s="71"/>
       <c r="AV5" s="18" t="s">
         <v>14</v>
       </c>
@@ -2057,6 +2057,15 @@
   </sheetData>
   <autoFilter ref="A5:BB5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="18">
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="AT4:AT5"/>
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AI4:AI5"/>
     <mergeCell ref="AJ4:AJ5"/>
@@ -2066,15 +2075,6 @@
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AM4:AM5"/>
-    <mergeCell ref="AN4:AN5"/>
-    <mergeCell ref="AO4:AO5"/>
-    <mergeCell ref="AP4:AP5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AQ4:AQ5"/>
-    <mergeCell ref="AR4:AR5"/>
-    <mergeCell ref="AS4:AS5"/>
-    <mergeCell ref="AT4:AT5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A6:BA6">

--- a/doctool/Excel設計書レビュー指摘事項抽出ツール/レビュー記録サマリ.xlsx
+++ b/doctool/Excel設計書レビュー指摘事項抽出ツール/レビュー記録サマリ.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A045EE-3E34-4828-A8EA-3776A2166E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6CAD9-28E1-4B4D-BD2A-26872ABD232D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品質指標" sheetId="4" r:id="rId1"/>
@@ -13,12 +13,12 @@
     <sheet name="List" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">レビュー記録一覧!$A$5:$AR$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">レビュー記録一覧!$A$5:$BB$5</definedName>
     <definedName name="Method">List!$C$2:$C$3</definedName>
     <definedName name="Necessity">List!$F$2:$F$3</definedName>
     <definedName name="Person">List!#REF!</definedName>
     <definedName name="Phase">List!$A$2:$A$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー記録一覧!$A$1:$AN$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー記録一覧!$A$1:$AX$23</definedName>
     <definedName name="Result">List!$E$2:$E$4</definedName>
     <definedName name="Time">List!$D$2:$D$3</definedName>
     <definedName name="Volume">List!$B$2:$B$4</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="88">
   <si>
     <t>対象成果物</t>
     <rPh sb="0" eb="2">
@@ -52,16 +52,6 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>ブツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>指摘事項</t>
-    <rPh sb="0" eb="2">
-      <t>シテキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジコウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -675,6 +665,32 @@
   </si>
   <si>
     <t>i)93_仕様変更</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>未済指摘事項</t>
+    <rPh sb="0" eb="2">
+      <t>ミサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全指摘事項</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジコウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -757,7 +773,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,6 +810,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -975,7 +997,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1062,7 +1084,7 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1102,6 +1124,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1119,15 +1152,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準_レビュー記録サマリ_20130709" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="lightTrellis">
-          <fgColor indexed="22"/>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="lightTrellis">
@@ -1150,9 +1175,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1190,9 +1215,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1225,26 +1250,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1277,26 +1285,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1487,50 +1478,50 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="25" t="s">
         <v>53</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1541,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A7,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G7" s="22">
@@ -1551,14 +1542,14 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1569,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A8,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G8" s="22">
@@ -1579,14 +1570,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1597,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A9,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G9" s="22">
@@ -1607,14 +1598,14 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1625,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A10,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G10" s="22">
@@ -1635,14 +1626,14 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AR$6:$AR$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$BB$6:$BB$152)</f>
         <v>0</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="27">
         <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AA$6:$AA$152)</f>
@@ -1653,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="23">
-        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AB$6:$AB$152)</f>
+        <f>SUMIF(レビュー記録一覧!$C$6:$C$152,品質指標!$A11,レビュー記録一覧!$AL$6:$AL$152)</f>
         <v>0</v>
       </c>
       <c r="G11" s="22">
@@ -1674,7 +1665,7 @@
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.625" style="1" bestFit="1" customWidth="1"/>
@@ -1701,63 +1692,65 @@
     <col min="26" max="27" width="9.25" style="1" customWidth="1"/>
     <col min="28" max="28" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="37" width="11.125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="11.25" style="1" customWidth="1"/>
-    <col min="39" max="39" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="39.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.125" style="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="9" style="1"/>
+    <col min="38" max="38" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="47" width="11.125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="11.25" style="1" customWidth="1"/>
+    <col min="49" max="49" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="39.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.125" style="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="AM1" s="5" t="s">
+      <c r="AW1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="AW2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AN1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="AM2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.15">
+      <c r="AX2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="D3" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" s="37"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
       <c r="AA3" s="21"/>
-      <c r="AP3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AZ3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>0</v>
@@ -1776,7 +1769,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
@@ -1788,118 +1781,148 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="10"/>
-      <c r="AB4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="64" t="s">
+      <c r="AB4" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC4" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD4" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="AD4" s="66" t="s">
+      <c r="AE4" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="AE4" s="66" t="s">
+      <c r="AF4" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG4" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="AF4" s="66" t="s">
+      <c r="AH4" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI4" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ4" s="66" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK4" s="66" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL4" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM4" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="AG4" s="66" t="s">
+      <c r="AN4" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO4" s="71" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP4" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ4" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR4" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="AH4" s="66" t="s">
+      <c r="AS4" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="AI4" s="66" t="s">
+      <c r="AT4" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="AJ4" s="66" t="s">
+      <c r="AU4" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="AK4" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="6"/>
-      <c r="AO4" s="10"/>
-      <c r="AP4" s="31" t="s">
+      <c r="AV4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="9"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA4" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="AQ4" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="AR4" s="34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44" ht="27" x14ac:dyDescent="0.15">
+      <c r="BB4" s="34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="17"/>
       <c r="L5" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
       <c r="P5" s="63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="9"/>
       <c r="W5" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="17"/>
       <c r="Y5" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB5" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC5" s="65"/>
+        <v>44</v>
+      </c>
+      <c r="AB5" s="65" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC5" s="68"/>
       <c r="AD5" s="66"/>
       <c r="AE5" s="66"/>
       <c r="AF5" s="66"/>
@@ -1908,35 +1931,47 @@
       <c r="AI5" s="66"/>
       <c r="AJ5" s="66"/>
       <c r="AK5" s="66"/>
-      <c r="AL5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM5" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO5" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP5" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ5" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR5" s="34" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.15">
+      <c r="AL5" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="AM5" s="70"/>
+      <c r="AN5" s="71"/>
+      <c r="AO5" s="71"/>
+      <c r="AP5" s="71"/>
+      <c r="AQ5" s="71"/>
+      <c r="AR5" s="71"/>
+      <c r="AS5" s="71"/>
+      <c r="AT5" s="71"/>
+      <c r="AU5" s="71"/>
+      <c r="AV5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AY5" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="AZ5" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BA5" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB5" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A6" s="40">
         <f t="shared" ref="A6" si="0">ROW()-5</f>
         <v>1</v>
       </c>
       <c r="B6" s="41" t="str">
-        <f>IF(C6&lt;&gt;"",IF(OR(AND(AL6&lt;&gt;"",AL6&lt;&gt;"再レビュー要"),COUNTIF(I$6:I16,A6)&gt;0),"○",""),"")</f>
+        <f>IF(C6&lt;&gt;"",IF(OR(AND(AV6&lt;&gt;"",AV6&lt;&gt;"再レビュー要"),COUNTIF(I$6:I16,A6)&gt;0),"○",""),"")</f>
         <v/>
       </c>
       <c r="C6" s="42"/>
@@ -1948,12 +1983,12 @@
       <c r="I6" s="46"/>
       <c r="J6" s="47"/>
       <c r="K6" s="45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="49"/>
       <c r="N6" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O6" s="49"/>
       <c r="P6" s="51">
@@ -1989,43 +2024,60 @@
       <c r="AI6" s="59"/>
       <c r="AJ6" s="59"/>
       <c r="AK6" s="59"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="60"/>
-      <c r="AO6" s="61"/>
-      <c r="AP6" s="62" t="str">
-        <f t="shared" ref="AP6" si="3">IF(J6&lt;&gt;"",AA6/(J6*AO6/10),"")</f>
+      <c r="AL6" s="58">
+        <f t="shared" ref="AL6" si="3">SUM(AM6:AU6)</f>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="42"/>
+      <c r="AW6" s="42"/>
+      <c r="AX6" s="60"/>
+      <c r="AY6" s="61"/>
+      <c r="AZ6" s="62" t="str">
+        <f>IF(J6&lt;&gt;"",AA6/(J6*AY6/10),"")</f>
         <v/>
       </c>
-      <c r="AQ6" s="62" t="str">
-        <f t="shared" ref="AQ6" si="4">IF(J6&lt;&gt;"",AB6/(J6*AO6/10),"")</f>
+      <c r="BA6" s="62" t="str">
+        <f>IF(J6&lt;&gt;"",AB6/(J6*AY6/10),"")</f>
         <v/>
       </c>
-      <c r="AR6" s="2" t="str">
-        <f t="shared" ref="AR6" si="5">IF(H6=1,J6*AO6,"")</f>
+      <c r="BB6" s="2" t="str">
+        <f t="shared" ref="BB6" si="4">IF(H6=1,J6*AY6,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AR5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <mergeCells count="9">
+  <autoFilter ref="A5:BB5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <mergeCells count="18">
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="AN4:AN5"/>
+    <mergeCell ref="AO4:AO5"/>
+    <mergeCell ref="AP4:AP5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AQ4:AQ5"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AS4:AS5"/>
+    <mergeCell ref="AT4:AT5"/>
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AI4:AI5"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AK4:AK5"/>
     <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="AI4:AI5"/>
-    <mergeCell ref="AJ4:AJ5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="AM6:AQ6 A6:AK6">
-    <cfRule type="expression" dxfId="1" priority="105" stopIfTrue="1">
-      <formula>$B6="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL6">
+  <conditionalFormatting sqref="A6:BA6">
     <cfRule type="expression" dxfId="0" priority="103" stopIfTrue="1">
       <formula>$B6="○"</formula>
     </cfRule>
@@ -2040,15 +2092,15 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y6" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>Method</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM6" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW6" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>Necessity</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL6" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV6" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>Result</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.46" right="0.43" top="0.66" bottom="0.49" header="0.51200000000000001" footer="0.28999999999999998"/>
-  <pageSetup paperSize="9" scale="34" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="26" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader xml:space="preserve">&amp;R【&amp;U関係者外秘：SSMSアプリ開発PJメンバー限り&amp;U】 </oddHeader>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
@@ -2068,103 +2120,103 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
